--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488188_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488188_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8803</v>
+        <v>1.5971</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3646</v>
+        <v>2.9089</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4842</v>
+        <v>-1.3119</v>
       </c>
       <c r="G2" t="n">
         <v>1.3002</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3463</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1554</v>
+        <v>0.3889</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1908</v>
+        <v>-1.0185</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.451</v>
+        <v>0.3711</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0527</v>
+        <v>2.8251</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.6017</v>
+        <v>-2.454</v>
       </c>
       <c r="G3" t="n">
         <v>-3.257</v>
@@ -688,13 +688,13 @@
         <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7265</v>
+        <v>0.6466</v>
       </c>
       <c r="T3" t="n">
-        <v>1.593</v>
+        <v>1.3654</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8665</v>
+        <v>-0.7188</v>
       </c>
       <c r="V3" t="n">
         <v>0.9433</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SINATRA VAZQUEZ</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1898</v>
+        <v>0.2875</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6499</v>
+        <v>3.3877</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8397</v>
+        <v>-3.1002</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6623</v>
+        <v>-1.9562</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1647</v>
+        <v>-4.2339</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4977</v>
+        <v>2.2776</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1262</v>
+        <v>3.5257</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2198</v>
+        <v>-0.3952</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0936</v>
+        <v>3.9209</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5361</v>
+        <v>-5.4819</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0552</v>
+        <v>-3.8387</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5913</v>
+        <v>-1.6433</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>2.2234</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>3.1499</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1845</v>
+        <v>-0.2947</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4763</v>
+        <v>0.7884</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2917</v>
+        <v>-1.0831</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. POL RUBIO</t>
+          <t>M. SINATRA VAZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1193</v>
+        <v>0.239</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0955</v>
+        <v>-0.6499</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0237</v>
+        <v>0.889</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7824</v>
+        <v>-1.6623</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8838</v>
+        <v>-1.1647</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1014</v>
+        <v>-0.4977</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.507</v>
+        <v>-1.1262</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6314</v>
+        <v>-1.2198</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1244</v>
+        <v>0.0936</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2754</v>
+        <v>-0.5361</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2524</v>
+        <v>0.0552</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.023</v>
+        <v>-0.5913</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3925</v>
+        <v>0.2338</v>
       </c>
       <c r="T6" t="n">
-        <v>0.097</v>
+        <v>0.4763</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4895</v>
+        <v>-0.2425</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>D. POL RUBIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6601</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4401</v>
+        <v>-0.0955</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1002</v>
+        <v>0.0255</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9562</v>
+        <v>-0.7824</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.2339</v>
+        <v>-0.8838</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2776</v>
+        <v>0.1014</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5257</v>
+        <v>-0.507</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3952</v>
+        <v>-0.6314</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9209</v>
+        <v>0.1244</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.4819</v>
+        <v>-0.2754</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.8387</v>
+        <v>-0.2524</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6433</v>
+        <v>-0.023</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1499</v>
+        <v>0.7411</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2423</v>
+        <v>-0.3432</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1591</v>
+        <v>0.097</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0831</v>
+        <v>-0.4402</v>
       </c>
       <c r="V7" t="n">
-        <v>0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2096</v>
+        <v>-1.6352</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0512</v>
+        <v>1.0195</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2607</v>
+        <v>-2.6547</v>
       </c>
       <c r="G8" t="n">
         <v>-4.2881</v>
@@ -1078,13 +1078,13 @@
         <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4698</v>
+        <v>0.0441</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6156</v>
+        <v>0.5839</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1458</v>
+        <v>-0.5397</v>
       </c>
       <c r="V8" t="n">
         <v>4.091</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0223</v>
+        <v>-2.4266</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0747</v>
+        <v>-0.4035</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.097</v>
+        <v>-2.0231</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6223</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0267</v>
+        <v>0.6224</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8666</v>
+        <v>1.3884</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8399</v>
+        <v>-0.766</v>
       </c>
       <c r="V9" t="n">
         <v>0.3144</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>P. SECO LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6361</v>
+        <v>-4.4373</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1985</v>
+        <v>-3.2519</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4376</v>
+        <v>-1.1854</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.0086</v>
+        <v>-4.1254</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.1854</v>
+        <v>-1.2975</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.8232</v>
+        <v>-2.8278</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.6733</v>
+        <v>-1.1033</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1863</v>
+        <v>0.1503</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.487</v>
+        <v>-1.2536</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3352</v>
+        <v>-3.0221</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9991</v>
+        <v>-1.4478</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3361</v>
+        <v>-1.5743</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9646</v>
+        <v>0.1853</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.5586</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>2.594</v>
+        <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6161</v>
+        <v>0.1328</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9424</v>
+        <v>0.3342</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3263</v>
+        <v>-0.2015</v>
       </c>
       <c r="V11" t="n">
-        <v>4.721</v>
+        <v>-0.63</v>
       </c>
       <c r="W11" t="n">
-        <v>4.091</v>
+        <v>-0.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. SECO LOPEZ</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4473</v>
+        <v>-4.6783</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.188</v>
+        <v>-4.0684</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2593</v>
+        <v>-0.6099</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1254</v>
+        <v>-7.0086</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2975</v>
+        <v>-3.1854</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8278</v>
+        <v>-3.8232</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1033</v>
+        <v>-3.6733</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1503</v>
+        <v>-1.1863</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2536</v>
+        <v>-2.487</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0221</v>
+        <v>-3.3352</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4478</v>
+        <v>-1.9991</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5743</v>
+        <v>-1.3361</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1853</v>
+        <v>-2.9646</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8529</v>
+        <v>-5.5586</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0382</v>
+        <v>2.594</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8772</v>
+        <v>0.5739</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6019</v>
+        <v>1.0726</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2753</v>
+        <v>-0.4987</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.63</v>
+        <v>4.721</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.63</v>
+        <v>4.091</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.0459</v>
+        <v>-13.225</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7472999999999992</v>
+        <v>0.0732999999999997</v>
       </c>
       <c r="F13" t="n">
         <v>-13.2983</v>
@@ -1447,7 +1447,7 @@
         <v>-0.8271999999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9935</v>
+        <v>2.993499999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-26.8716</v>
@@ -1459,7 +1459,7 @@
         <v>-8.984200000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9264000000000003</v>
+        <v>0.9264000000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.6022</v>
@@ -1468,13 +1468,13 @@
         <v>18.5288</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3357999999999999</v>
+        <v>0.4850999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>5.5651</v>
+        <v>6.3857</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.9006</v>
+        <v>-5.900700000000001</v>
       </c>
       <c r="V13" t="n">
         <v>10.0691</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.0946</v>
+        <v>7.7667</v>
       </c>
       <c r="E14" t="n">
-        <v>7.8276</v>
+        <v>5.4773</v>
       </c>
       <c r="F14" t="n">
-        <v>2.267</v>
+        <v>2.2894</v>
       </c>
       <c r="G14" t="n">
         <v>4.2038</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1671</v>
+        <v>1.8392</v>
       </c>
       <c r="T14" t="n">
-        <v>4.4233</v>
+        <v>2.073</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2562</v>
+        <v>-0.2338</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3144</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5402</v>
+        <v>4.9698</v>
       </c>
       <c r="E15" t="n">
-        <v>1.569</v>
+        <v>2.2545</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9712</v>
+        <v>2.7153</v>
       </c>
       <c r="G15" t="n">
         <v>4.3077</v>
@@ -1624,13 +1624,13 @@
         <v>2.7793</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1943</v>
+        <v>0.2353</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0174</v>
+        <v>0.7029</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2117</v>
+        <v>-0.4676</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3144</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6765</v>
+        <v>3.9933</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8695000000000001</v>
+        <v>2.9114</v>
       </c>
       <c r="F16" t="n">
-        <v>1.807</v>
+        <v>1.0819</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5099</v>
+        <v>5.7206</v>
       </c>
       <c r="H16" t="n">
-        <v>3.805</v>
+        <v>4.8357</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.295</v>
+        <v>0.8849</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4512</v>
+        <v>5.4871</v>
       </c>
       <c r="K16" t="n">
-        <v>4.04</v>
+        <v>4.5949</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5888</v>
+        <v>0.8923</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9412</v>
+        <v>0.2335</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.235</v>
+        <v>0.2409</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7063</v>
+        <v>-0.0074</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.4823</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.6322</v>
+        <v>-2.9646</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1499</v>
+        <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3338</v>
+        <v>-0.2276</v>
       </c>
       <c r="T16" t="n">
-        <v>1.736</v>
+        <v>0.7039</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4022</v>
+        <v>-0.9314</v>
       </c>
       <c r="V16" t="n">
-        <v>0.315</v>
+        <v>-0.9439</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0005</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4883</v>
+        <v>3.9549</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6794</v>
+        <v>1.9321</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1912</v>
+        <v>2.0228</v>
       </c>
       <c r="G17" t="n">
-        <v>4.3829</v>
+        <v>4.9757</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2234</v>
+        <v>3.1186</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1594</v>
+        <v>1.8572</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8983</v>
+        <v>5.4793</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.3536</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8983</v>
+        <v>2.1257</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4846</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2234</v>
+        <v>-0.235</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2611</v>
+        <v>-0.2686</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1853</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1853</v>
+        <v>-3.7057</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3706</v>
+        <v>2.2234</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.1685</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0336</v>
+        <v>0.1586</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.473</v>
+        <v>-0.3271</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5733</v>
+        <v>0.63</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5733</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4683</v>
+        <v>2.5621</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9528</v>
+        <v>3.6794</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5155</v>
+        <v>-1.1173</v>
       </c>
       <c r="G18" t="n">
-        <v>4.9757</v>
+        <v>4.3829</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1186</v>
+        <v>0.2234</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8572</v>
+        <v>4.1594</v>
       </c>
       <c r="J18" t="n">
-        <v>5.4793</v>
+        <v>3.8983</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3536</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1257</v>
+        <v>3.8983</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5034999999999999</v>
+        <v>0.4846</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.235</v>
+        <v>0.2234</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2686</v>
+        <v>0.2611</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4823</v>
+        <v>0.1853</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.7057</v>
+        <v>-0.1853</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2234</v>
+        <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6552</v>
+        <v>-0.4328</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8207</v>
+        <v>-0.0336</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8344</v>
+        <v>-0.3992</v>
       </c>
       <c r="V18" t="n">
-        <v>0.63</v>
+        <v>-1.5733</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.63</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1883</v>
+        <v>2.4239</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1883</v>
+        <v>0.2819</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.142</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1883</v>
+        <v>2.5099</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3221</v>
+        <v>3.805</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8662</v>
+        <v>-1.295</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1883</v>
+        <v>3.4512</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3221</v>
+        <v>4.04</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8662</v>
+        <v>-0.5888</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.9412</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.235</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.7063</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.1499</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.0813</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.1484</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.0672</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.163</v>
+        <v>2.1883</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7362</v>
+        <v>2.1883</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4268</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>5.7206</v>
+        <v>2.1883</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8357</v>
+        <v>0.3221</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8849</v>
+        <v>1.8662</v>
       </c>
       <c r="J20" t="n">
-        <v>5.4871</v>
+        <v>2.1883</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5949</v>
+        <v>0.3221</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8923</v>
+        <v>1.8662</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2335</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2409</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0074</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9646</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0578</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4713</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.5865</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.067</v>
+        <v>-1.2056</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6743</v>
+        <v>0.3805</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7413</v>
+        <v>-1.5861</v>
       </c>
       <c r="G21" t="n">
         <v>0.0449</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.147</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6529</v>
+        <v>0.3591</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5059</v>
+        <v>-0.3507</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>U. CHAGOYEN SALGUERO</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6947</v>
+        <v>-1.4128</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0727</v>
+        <v>1.1749</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.622</v>
+        <v>-2.5877</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3296</v>
+        <v>0.5542</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.127</v>
+        <v>1.0626</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2027</v>
+        <v>-0.5083</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1784</v>
+        <v>1.2209</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2198</v>
+        <v>1.138</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>0.0829</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1513</v>
+        <v>-0.6667</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0929</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2441</v>
+        <v>-0.5913</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8202</v>
+        <v>0.0684</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0321</v>
+        <v>-0.046</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2119</v>
+        <v>0.1144</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-3.1471</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-3.1471</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>U. CHAGOYEN SALGUERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7135</v>
+        <v>-2.0778</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7832</v>
+        <v>-1.6602</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4967</v>
+        <v>-0.4176</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5542</v>
+        <v>-2.3296</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0626</v>
+        <v>-1.127</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5083</v>
+        <v>-1.2027</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2209</v>
+        <v>-1.1784</v>
       </c>
       <c r="K23" t="n">
-        <v>1.138</v>
+        <v>-1.2198</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0829</v>
+        <v>0.0415</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6667</v>
+        <v>-1.1513</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.0929</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5913</v>
+        <v>-1.2441</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2323</v>
+        <v>0.4371</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4377</v>
+        <v>0.4446</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2054</v>
+        <v>-0.0075</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.1471</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.1471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1278</v>
+        <v>-2.0786</v>
       </c>
       <c r="E24" t="n">
         <v>-0.7602</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3676</v>
+        <v>-1.3184</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4568</v>
@@ -2326,13 +2326,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4683</v>
+        <v>-0.4191</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3589</v>
+        <v>-0.3096</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5733</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9704</v>
+        <v>-5.0799</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1492</v>
+        <v>-4.5616</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8212</v>
+        <v>-0.5183</v>
       </c>
       <c r="G25" t="n">
         <v>-1.396</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.018</v>
+        <v>-0.1275</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0883</v>
+        <v>0.4993</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9297</v>
+        <v>-0.6268</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8888</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>14.0458</v>
+        <v>16.00429999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>13.2982</v>
+        <v>13.2983</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7474999999999997</v>
+        <v>2.706000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>24.7056</v>
@@ -2482,13 +2482,13 @@
         <v>17.6022</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3355999999999999</v>
+        <v>2.2942</v>
       </c>
       <c r="T26" t="n">
-        <v>5.9007</v>
+        <v>5.900799999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.565</v>
+        <v>-3.6065</v>
       </c>
       <c r="V26" t="n">
         <v>-10.0691</v>
